--- a/Documents/Product Catalog/Office/Visitor Chair  Specifications.xlsx
+++ b/Documents/Product Catalog/Office/Visitor Chair  Specifications.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Product Price List\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="d:\Talukder Furniture\Documents\Product Catalog\Office\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7D69058-DA81-4825-AD0F-FE23E2632FAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12435"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Visitor Chair " sheetId="14" r:id="rId1"/>
@@ -17,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Visitor Chair '!$B$1:$R$21</definedName>
   </definedNames>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -26,6 +27,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -923,7 +926,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="12">
     <font>
       <sz val="10"/>
@@ -1218,24 +1221,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="8" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="8" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="8" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1254,10 +1239,28 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="8" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="8" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="8" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1297,7 +1300,7 @@
         <xdr:cNvPr id="2" name="image1.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1347,7 +1350,7 @@
         <xdr:cNvPr id="110" name="image108.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-0000C2010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-0000C2010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1397,7 +1400,7 @@
         <xdr:cNvPr id="111" name="image109.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-0000C3010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-0000C3010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1447,7 +1450,7 @@
         <xdr:cNvPr id="112" name="image110.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-0000C4010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-0000C4010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1497,7 +1500,7 @@
         <xdr:cNvPr id="113" name="image111.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-0000C5010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-0000C5010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1547,7 +1550,7 @@
         <xdr:cNvPr id="114" name="image112.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-0000C6010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-0000C6010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1597,7 +1600,7 @@
         <xdr:cNvPr id="115" name="image113.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-0000C7010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-0000C7010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1647,7 +1650,7 @@
         <xdr:cNvPr id="116" name="image114.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-0000C8010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-0000C8010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1697,7 +1700,7 @@
         <xdr:cNvPr id="117" name="image115.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-0000C9010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-0000C9010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1747,7 +1750,7 @@
         <xdr:cNvPr id="118" name="image116.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-0000CA010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-0000CA010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1797,7 +1800,7 @@
         <xdr:cNvPr id="119" name="image117.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-0000CB010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-0000CB010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1847,7 +1850,7 @@
         <xdr:cNvPr id="120" name="image118.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-0000CC010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-0000CC010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1897,7 +1900,7 @@
         <xdr:cNvPr id="121" name="image119.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-0000CD010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-0000CD010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1947,7 +1950,7 @@
         <xdr:cNvPr id="122" name="image120.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-0000CE010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-0000CE010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1997,7 +2000,7 @@
         <xdr:cNvPr id="123" name="image121.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-0000CF010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-0000CF010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2047,7 +2050,7 @@
         <xdr:cNvPr id="124" name="image122.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-0000D0010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-0000D0010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2097,7 +2100,7 @@
         <xdr:cNvPr id="125" name="image123.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-0000D1010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-0000D1010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2133,9 +2136,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2173,9 +2176,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2210,7 +2213,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2245,7 +2248,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2418,7 +2421,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B1:AT21"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
@@ -2441,89 +2444,89 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:46" ht="40.5" customHeight="1">
-      <c r="B1" s="20" t="s">
+      <c r="B1" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20"/>
-      <c r="K1" s="20"/>
-      <c r="L1" s="20"/>
-      <c r="M1" s="20"/>
-      <c r="N1" s="20"/>
-      <c r="O1" s="20"/>
-      <c r="P1" s="20"/>
-      <c r="Q1" s="20"/>
-      <c r="R1" s="21"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="14"/>
+      <c r="J1" s="14"/>
+      <c r="K1" s="14"/>
+      <c r="L1" s="14"/>
+      <c r="M1" s="14"/>
+      <c r="N1" s="14"/>
+      <c r="O1" s="14"/>
+      <c r="P1" s="14"/>
+      <c r="Q1" s="14"/>
+      <c r="R1" s="15"/>
     </row>
     <row r="2" spans="2:46" ht="39.950000000000003" customHeight="1">
-      <c r="B2" s="22" t="s">
+      <c r="B2" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
-      <c r="I2" s="22"/>
-      <c r="J2" s="22"/>
-      <c r="K2" s="22"/>
-      <c r="L2" s="22"/>
-      <c r="M2" s="22"/>
-      <c r="N2" s="22"/>
-      <c r="O2" s="22"/>
-      <c r="P2" s="22"/>
-      <c r="Q2" s="22"/>
-      <c r="R2" s="23"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
+      <c r="I2" s="16"/>
+      <c r="J2" s="16"/>
+      <c r="K2" s="16"/>
+      <c r="L2" s="16"/>
+      <c r="M2" s="16"/>
+      <c r="N2" s="16"/>
+      <c r="O2" s="16"/>
+      <c r="P2" s="16"/>
+      <c r="Q2" s="16"/>
+      <c r="R2" s="17"/>
     </row>
     <row r="3" spans="2:46" ht="50.1" customHeight="1">
-      <c r="B3" s="24" t="s">
+      <c r="B3" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="17" t="s">
+      <c r="C3" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="17" t="s">
+      <c r="D3" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="26" t="s">
+      <c r="E3" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="26" t="s">
+      <c r="F3" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="G3" s="17" t="s">
+      <c r="G3" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="17"/>
-      <c r="I3" s="17"/>
-      <c r="J3" s="17" t="s">
+      <c r="H3" s="20"/>
+      <c r="I3" s="20"/>
+      <c r="J3" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="K3" s="26" t="s">
+      <c r="K3" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="L3" s="17" t="s">
+      <c r="L3" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="M3" s="17"/>
-      <c r="N3" s="18"/>
-      <c r="O3" s="19" t="s">
+      <c r="M3" s="20"/>
+      <c r="N3" s="26"/>
+      <c r="O3" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="P3" s="17" t="s">
+      <c r="P3" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="Q3" s="17" t="s">
+      <c r="Q3" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="R3" s="17" t="s">
+      <c r="R3" s="20" t="s">
         <v>50</v>
       </c>
       <c r="S3" s="2"/>
@@ -2556,11 +2559,11 @@
       <c r="AT3" s="2"/>
     </row>
     <row r="4" spans="2:46" ht="33.200000000000003" customHeight="1">
-      <c r="B4" s="25"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="27"/>
-      <c r="F4" s="27"/>
+      <c r="B4" s="19"/>
+      <c r="C4" s="20"/>
+      <c r="D4" s="20"/>
+      <c r="E4" s="22"/>
+      <c r="F4" s="22"/>
       <c r="G4" s="12" t="s">
         <v>11</v>
       </c>
@@ -2570,8 +2573,8 @@
       <c r="I4" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="J4" s="17"/>
-      <c r="K4" s="27"/>
+      <c r="J4" s="20"/>
+      <c r="K4" s="22"/>
       <c r="L4" s="1" t="s">
         <v>3</v>
       </c>
@@ -2581,10 +2584,10 @@
       <c r="N4" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="O4" s="19"/>
-      <c r="P4" s="19"/>
-      <c r="Q4" s="19"/>
-      <c r="R4" s="19"/>
+      <c r="O4" s="27"/>
+      <c r="P4" s="27"/>
+      <c r="Q4" s="27"/>
+      <c r="R4" s="27"/>
       <c r="S4" s="2"/>
       <c r="T4" s="2"/>
       <c r="U4" s="2"/>
@@ -2615,25 +2618,25 @@
       <c r="AT4" s="2"/>
     </row>
     <row r="5" spans="2:46" ht="50.1" customHeight="1">
-      <c r="B5" s="14" t="s">
+      <c r="B5" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="15"/>
-      <c r="D5" s="15"/>
-      <c r="E5" s="15"/>
-      <c r="F5" s="15"/>
-      <c r="G5" s="15"/>
-      <c r="H5" s="15"/>
-      <c r="I5" s="15"/>
-      <c r="J5" s="15"/>
-      <c r="K5" s="15"/>
-      <c r="L5" s="15"/>
-      <c r="M5" s="15"/>
-      <c r="N5" s="15"/>
-      <c r="O5" s="15"/>
-      <c r="P5" s="15"/>
-      <c r="Q5" s="15"/>
-      <c r="R5" s="16"/>
+      <c r="C5" s="24"/>
+      <c r="D5" s="24"/>
+      <c r="E5" s="24"/>
+      <c r="F5" s="24"/>
+      <c r="G5" s="24"/>
+      <c r="H5" s="24"/>
+      <c r="I5" s="24"/>
+      <c r="J5" s="24"/>
+      <c r="K5" s="24"/>
+      <c r="L5" s="24"/>
+      <c r="M5" s="24"/>
+      <c r="N5" s="24"/>
+      <c r="O5" s="24"/>
+      <c r="P5" s="24"/>
+      <c r="Q5" s="24"/>
+      <c r="R5" s="25"/>
     </row>
     <row r="6" spans="2:46" ht="80.099999999999994" customHeight="1">
       <c r="B6" s="3">
@@ -2822,10 +2825,10 @@
       </c>
       <c r="L9" s="7">
         <f t="shared" si="0"/>
-        <v>5580</v>
+        <v>5220</v>
       </c>
       <c r="M9" s="9">
-        <v>6200</v>
+        <v>5800</v>
       </c>
       <c r="N9" s="6">
         <v>0.1</v>
@@ -2874,10 +2877,10 @@
       </c>
       <c r="L10" s="7">
         <f t="shared" si="0"/>
-        <v>4950</v>
+        <v>4050</v>
       </c>
       <c r="M10" s="9">
-        <v>5500</v>
+        <v>4500</v>
       </c>
       <c r="N10" s="6">
         <v>0.1</v>
@@ -2926,10 +2929,10 @@
       </c>
       <c r="L11" s="7">
         <f t="shared" si="0"/>
-        <v>4140</v>
+        <v>3420</v>
       </c>
       <c r="M11" s="9">
-        <v>4600</v>
+        <v>3800</v>
       </c>
       <c r="N11" s="6">
         <v>0.1</v>
@@ -3082,10 +3085,10 @@
       </c>
       <c r="L14" s="7">
         <f t="shared" si="0"/>
-        <v>7200</v>
+        <v>5760</v>
       </c>
       <c r="M14" s="9">
-        <v>8000</v>
+        <v>6400</v>
       </c>
       <c r="N14" s="6">
         <v>0.1</v>
@@ -3134,10 +3137,10 @@
       </c>
       <c r="L15" s="7">
         <f t="shared" si="0"/>
-        <v>2835</v>
+        <v>3330</v>
       </c>
       <c r="M15" s="9">
-        <v>3150</v>
+        <v>3700</v>
       </c>
       <c r="N15" s="6">
         <v>0.1</v>
@@ -3186,10 +3189,10 @@
       </c>
       <c r="L16" s="7">
         <f t="shared" si="0"/>
-        <v>2655</v>
+        <v>2520</v>
       </c>
       <c r="M16" s="9">
-        <v>2950</v>
+        <v>2800</v>
       </c>
       <c r="N16" s="6">
         <v>0.1</v>
@@ -3238,10 +3241,10 @@
       </c>
       <c r="L17" s="7">
         <f t="shared" si="0"/>
-        <v>4140</v>
+        <v>3960</v>
       </c>
       <c r="M17" s="9">
-        <v>4600</v>
+        <v>4400</v>
       </c>
       <c r="N17" s="6">
         <v>0.1</v>
@@ -3290,10 +3293,10 @@
       </c>
       <c r="L18" s="7">
         <f t="shared" si="0"/>
-        <v>6300</v>
+        <v>9450</v>
       </c>
       <c r="M18" s="9">
-        <v>7000</v>
+        <v>10500</v>
       </c>
       <c r="N18" s="6">
         <v>0.1</v>
@@ -3394,10 +3397,10 @@
       </c>
       <c r="L20" s="7">
         <f t="shared" si="0"/>
-        <v>5850</v>
+        <v>5130</v>
       </c>
       <c r="M20" s="9">
-        <v>6500</v>
+        <v>5700</v>
       </c>
       <c r="N20" s="6">
         <v>0.1</v>
@@ -3469,6 +3472,12 @@
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="B5:R5"/>
+    <mergeCell ref="L3:N3"/>
+    <mergeCell ref="O3:O4"/>
+    <mergeCell ref="P3:P4"/>
+    <mergeCell ref="Q3:Q4"/>
+    <mergeCell ref="R3:R4"/>
     <mergeCell ref="B1:R1"/>
     <mergeCell ref="B2:R2"/>
     <mergeCell ref="B3:B4"/>
@@ -3479,12 +3488,6 @@
     <mergeCell ref="G3:I3"/>
     <mergeCell ref="J3:J4"/>
     <mergeCell ref="K3:K4"/>
-    <mergeCell ref="B5:R5"/>
-    <mergeCell ref="L3:N3"/>
-    <mergeCell ref="O3:O4"/>
-    <mergeCell ref="P3:P4"/>
-    <mergeCell ref="Q3:Q4"/>
-    <mergeCell ref="R3:R4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="10" orientation="portrait" r:id="rId1"/>
